--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-precondition-extension.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-precondition-extension.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Fr Précondition de l'administration</t>
+    <t>Extension - Fr Précondition de l'administration</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Lien vers la description narrative des conditions préalables dans le document CDA.</t>
+    <t>Extension permettant d'indiquer le lien vers la description narrative des conditions préalables dans le document.</t>
   </si>
   <si>
     <t>Purpose</t>
